--- a/informe-c/base_dolares.xlsx
+++ b/informe-c/base_dolares.xlsx
@@ -13,8 +13,8 @@
     <sheet sheetId="5" name="Activo y Pasivo" state="visible" r:id="rId7"/>
     <sheet sheetId="12" name="Anexo I" state="visible" r:id="rId8"/>
     <sheet sheetId="10" name="Anexo II" state="visible" r:id="rId9"/>
-    <sheet sheetId="11" name="SALDOS" state="hidden" r:id="rId10"/>
-    <sheet sheetId="13" name="Hoja1" state="hidden" r:id="rId11"/>
+    <sheet sheetId="11" name="Distribución por línea" state="hidden" r:id="rId10"/>
+    <sheet sheetId="13" name="Balance de sumas y saldos" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Anexo II'!$E$9:$E$102</definedName>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Anexo I'!$A1:$K36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Anexo II'!$A2:$J112</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -3959,7 +3959,7 @@
       <c r="F10" s="116"/>
       <c r="G10" s="11"/>
       <c r="H10" s="12">
-        <f>+SALDOS!C164</f>
+        <f>+'Distribución por línea'!C164</f>
         <v>36709.74</v>
       </c>
       <c r="I10" s="117"/>
@@ -3980,7 +3980,7 @@
         <v>185113.95</v>
       </c>
       <c r="F11" s="12">
-        <f>+SALDOS!C175+SALDOS!C205</f>
+        <f>+'Distribución por línea'!C175+'Distribución por línea'!C205</f>
         <v>185113.95</v>
       </c>
       <c r="G11" s="11"/>
@@ -4005,7 +4005,7 @@
       <c r="F12" s="116"/>
       <c r="G12" s="11"/>
       <c r="H12" s="12">
-        <f>+SALDOS!C176</f>
+        <f>+'Distribución por línea'!C176</f>
         <v>41896.28</v>
       </c>
       <c r="I12" s="117"/>
@@ -4028,8 +4028,7 @@
       <c r="F13" s="116"/>
       <c r="G13" s="11"/>
       <c r="H13" s="12">
-        <f>+SALDOS!C144</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C144</f>
       </c>
       <c r="I13" s="117"/>
       <c r="J13" s="115"/>
@@ -4051,7 +4050,7 @@
       <c r="F14" s="116"/>
       <c r="G14" s="11"/>
       <c r="H14" s="12">
-        <f>+SALDOS!C156</f>
+        <f>+'Distribución por línea'!C156</f>
         <v>130.73</v>
       </c>
       <c r="I14" s="117"/>
@@ -4074,8 +4073,7 @@
       <c r="F15" s="116"/>
       <c r="G15" s="11"/>
       <c r="H15" s="12">
-        <f>+SALDOS!C186</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C186</f>
       </c>
       <c r="I15" s="117"/>
       <c r="J15" s="115"/>
@@ -4097,7 +4095,7 @@
       <c r="F16" s="116"/>
       <c r="G16" s="11"/>
       <c r="H16" s="12">
-        <f>+SALDOS!C123+SALDOS!C120</f>
+        <f>+'Distribución por línea'!C123+'Distribución por línea'!C120</f>
         <v>21.03</v>
       </c>
       <c r="I16" s="117"/>
@@ -4120,8 +4118,7 @@
       <c r="F17" s="116"/>
       <c r="G17" s="11"/>
       <c r="H17" s="12">
-        <f>+SALDOS!C160</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C160</f>
       </c>
       <c r="I17" s="117"/>
       <c r="J17" s="115"/>
@@ -4143,8 +4140,7 @@
       <c r="F18" s="116"/>
       <c r="G18" s="11"/>
       <c r="H18" s="12">
-        <f>+SALDOS!C170</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C170</f>
       </c>
       <c r="I18" s="117"/>
       <c r="J18" s="115"/>
@@ -4166,8 +4162,7 @@
       <c r="F19" s="116"/>
       <c r="G19" s="11"/>
       <c r="H19" s="12">
-        <f>+SALDOS!C171+SALDOS!C172</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C171+'Distribución por línea'!C172</f>
       </c>
       <c r="I19" s="117"/>
       <c r="J19" s="115"/>
@@ -4210,12 +4205,12 @@
         <v>46687.64</v>
       </c>
       <c r="F21" s="116">
-        <f>+SALDOS!C117</f>
+        <f>+'Distribución por línea'!C117</f>
         <v>10000.93</v>
       </c>
       <c r="G21" s="11"/>
       <c r="H21" s="12">
-        <f>+SALDOS!C192</f>
+        <f>+'Distribución por línea'!C192</f>
         <v>36686.71</v>
       </c>
       <c r="I21" s="117"/>
@@ -4238,7 +4233,7 @@
       <c r="F22" s="116"/>
       <c r="G22" s="11"/>
       <c r="H22" s="12">
-        <f>+SALDOS!C157+SALDOS!C222+SALDOS!C223+SALDOS!C229</f>
+        <f>+'Distribución por línea'!C157+'Distribución por línea'!C222+'Distribución por línea'!C223+'Distribución por línea'!C229</f>
         <v>34732.29</v>
       </c>
       <c r="I22" s="117"/>
@@ -4261,8 +4256,7 @@
       <c r="F23" s="116"/>
       <c r="G23" s="11"/>
       <c r="H23" s="12">
-        <f>+SALDOS!C187</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C187</f>
       </c>
       <c r="I23" s="117"/>
       <c r="J23" s="115"/>
@@ -4282,8 +4276,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="116">
-        <f>+SALDOS!C127</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C127</f>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="12"/>
@@ -4307,7 +4300,7 @@
       <c r="F25" s="116"/>
       <c r="G25" s="11"/>
       <c r="H25" s="12">
-        <f>+SALDOS!C169</f>
+        <f>+'Distribución por línea'!C169</f>
         <v>6051.11</v>
       </c>
       <c r="I25" s="117"/>
@@ -4330,7 +4323,7 @@
       <c r="F26" s="116"/>
       <c r="G26" s="11"/>
       <c r="H26" s="12">
-        <f>+SALDOS!C165</f>
+        <f>+'Distribución por línea'!C165</f>
         <v>19390</v>
       </c>
       <c r="I26" s="117"/>
@@ -4371,7 +4364,7 @@
         <v>5298.39</v>
       </c>
       <c r="F28" s="12">
-        <f>+SALDOS!C168</f>
+        <f>+'Distribución por línea'!C168</f>
         <v>5298.39</v>
       </c>
       <c r="G28" s="11"/>
@@ -4418,8 +4411,7 @@
       <c r="F30" s="116"/>
       <c r="G30" s="11"/>
       <c r="H30" s="12">
-        <f>+SALDOS!C159</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C159</f>
       </c>
       <c r="I30" s="117"/>
       <c r="J30" s="115"/>
@@ -4439,8 +4431,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="116">
-        <f>+SALDOS!C139</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C139</f>
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="12"/>
@@ -4464,8 +4455,7 @@
       <c r="F32" s="116"/>
       <c r="G32" s="11"/>
       <c r="H32" s="12">
-        <f>+SALDOS!C195</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C195</f>
       </c>
       <c r="I32" s="117"/>
       <c r="J32" s="115"/>
@@ -4485,8 +4475,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="12">
-        <f>+SALDOS!C204</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C204</f>
       </c>
       <c r="G33" s="11"/>
       <c r="H33" s="1"/>
@@ -4508,7 +4497,7 @@
         <v>346.02</v>
       </c>
       <c r="F34" s="118">
-        <f>+SALDOS!C188</f>
+        <f>+'Distribución por línea'!C188</f>
         <v>346.02</v>
       </c>
       <c r="G34" s="11"/>
@@ -4531,7 +4520,7 @@
         <v>6613.93</v>
       </c>
       <c r="F35" s="118">
-        <f>+SALDOS!C146</f>
+        <f>+'Distribución por línea'!C146</f>
         <v>6613.93</v>
       </c>
       <c r="G35" s="11"/>
@@ -4554,7 +4543,7 @@
         <v>7585.25</v>
       </c>
       <c r="F36" s="116">
-        <f>+SALDOS!C131+SALDOS!C124+SALDOS!C200</f>
+        <f>+'Distribución por línea'!C131+'Distribución por línea'!C124+'Distribución por línea'!C200</f>
         <v>7585.25</v>
       </c>
       <c r="G36" s="11"/>
@@ -4577,7 +4566,7 @@
         <v>10991.7</v>
       </c>
       <c r="F37" s="12">
-        <f>+SALDOS!C203</f>
+        <f>+'Distribución por línea'!C203</f>
         <v>10991.7</v>
       </c>
       <c r="G37" s="11"/>
@@ -4602,8 +4591,7 @@
       <c r="F38" s="116"/>
       <c r="G38" s="11"/>
       <c r="H38" s="12">
-        <f>+SALDOS!C196</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C196</f>
       </c>
       <c r="I38" s="117"/>
       <c r="J38" s="115"/>
@@ -4625,7 +4613,7 @@
       <c r="F39" s="116"/>
       <c r="G39" s="11"/>
       <c r="H39" s="12">
-        <f>+SALDOS!C198</f>
+        <f>+'Distribución por línea'!C198</f>
         <v>6055.09</v>
       </c>
       <c r="I39" s="117"/>
@@ -4648,7 +4636,7 @@
       <c r="F40" s="116"/>
       <c r="G40" s="11"/>
       <c r="H40" s="11">
-        <f>+SALDOS!C132</f>
+        <f>+'Distribución por línea'!C132</f>
         <v>3543.26</v>
       </c>
       <c r="I40" s="117"/>
@@ -4671,8 +4659,7 @@
       <c r="F41" s="116"/>
       <c r="G41" s="11"/>
       <c r="H41" s="12">
-        <f>+SALDOS!C138</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C138</f>
       </c>
       <c r="I41" s="117"/>
       <c r="J41" s="115"/>
@@ -4694,8 +4681,7 @@
       <c r="F42" s="116"/>
       <c r="G42" s="11"/>
       <c r="H42" s="12">
-        <f>+SALDOS!C173</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C173</f>
       </c>
       <c r="I42" s="117"/>
       <c r="J42" s="115"/>
@@ -4717,7 +4703,7 @@
       <c r="F43" s="116"/>
       <c r="G43" s="11"/>
       <c r="H43" s="12">
-        <f>+SALDOS!C161</f>
+        <f>+'Distribución por línea'!C161</f>
         <v>13.29</v>
       </c>
       <c r="I43" s="117"/>
@@ -4738,7 +4724,7 @@
         <v>2811.7</v>
       </c>
       <c r="F44" s="116">
-        <f>+SALDOS!C121</f>
+        <f>+'Distribución por línea'!C121</f>
         <v>2811.7</v>
       </c>
       <c r="G44" s="11"/>
@@ -4781,8 +4767,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="116">
-        <f>+SALDOS!C202</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C202</f>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="12"/>
@@ -4806,8 +4791,7 @@
       <c r="F47" s="1"/>
       <c r="G47" s="11"/>
       <c r="H47" s="116">
-        <f>+SALDOS!C143</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C143</f>
       </c>
       <c r="I47" s="117"/>
       <c r="J47" s="115"/>
@@ -4829,7 +4813,7 @@
       <c r="F48" s="116"/>
       <c r="G48" s="11"/>
       <c r="H48" s="12">
-        <f>+SALDOS!C189+SALDOS!C216</f>
+        <f>+'Distribución por línea'!C189+'Distribución por línea'!C216</f>
         <v>165115.85</v>
       </c>
       <c r="I48" s="117"/>
@@ -4850,8 +4834,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="116">
-        <f>+SALDOS!C136</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C136</f>
       </c>
       <c r="G49" s="11"/>
       <c r="H49" s="12"/>
@@ -4873,7 +4856,7 @@
         <v>10257.79</v>
       </c>
       <c r="F50" s="12">
-        <f>+SALDOS!C199</f>
+        <f>+'Distribución por línea'!C199</f>
         <v>10257.79</v>
       </c>
       <c r="G50" s="11"/>
@@ -4898,8 +4881,7 @@
       <c r="F51" s="116"/>
       <c r="G51" s="11"/>
       <c r="H51" s="12">
-        <f>+SALDOS!C135</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C135</f>
       </c>
       <c r="I51" s="117"/>
       <c r="J51" s="115"/>
@@ -4919,7 +4901,7 @@
         <v>6455.22</v>
       </c>
       <c r="F52" s="116">
-        <f>+SALDOS!C134+SALDOS!C174+SALDOS!C180+SALDOS!C183+SALDOS!C218</f>
+        <f>+'Distribución por línea'!C134+'Distribución por línea'!C174+'Distribución por línea'!C180+'Distribución por línea'!C183+'Distribución por línea'!C218</f>
         <v>6455.22</v>
       </c>
       <c r="G52" s="11"/>
@@ -4946,7 +4928,7 @@
       <c r="F53" s="116"/>
       <c r="G53" s="11"/>
       <c r="H53" s="12">
-        <f>+SALDOS!C155+SALDOS!C184</f>
+        <f>+'Distribución por línea'!C155+'Distribución por línea'!C184</f>
         <v>4667.97</v>
       </c>
       <c r="I53" s="117"/>
@@ -4969,8 +4951,7 @@
       <c r="F54" s="116"/>
       <c r="G54" s="11"/>
       <c r="H54" s="12">
-        <f>+SALDOS!C158</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C158</f>
       </c>
       <c r="I54" s="117"/>
       <c r="J54" s="115"/>
@@ -4990,8 +4971,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="116">
-        <f>+SALDOS!C113</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C113</f>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="12"/>
@@ -5013,7 +4993,7 @@
         <v>119655.77</v>
       </c>
       <c r="F56" s="116">
-        <f>+SALDOS!C114</f>
+        <f>+'Distribución por línea'!C114</f>
         <v>119655.77</v>
       </c>
       <c r="G56" s="11"/>
@@ -5036,7 +5016,7 @@
         <v>15857.28</v>
       </c>
       <c r="F57" s="118">
-        <f>+SALDOS!C147</f>
+        <f>+'Distribución por línea'!C147</f>
         <v>15857.28</v>
       </c>
       <c r="G57" s="11"/>
@@ -5059,8 +5039,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="118">
-        <f>+SALDOS!C148+SALDOS!C151+SALDOS!C122</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C148+'Distribución por línea'!C151+'Distribución por línea'!C122</f>
       </c>
       <c r="G58" s="11"/>
       <c r="H58" s="12"/>
@@ -5082,7 +5061,7 @@
         <v>8215.17</v>
       </c>
       <c r="F59" s="12">
-        <f>+SALDOS!C152+SALDOS!C115+SALDOS!C153+SALDOS!C220+SALDOS!C225</f>
+        <f>+'Distribución por línea'!C152+'Distribución por línea'!C115+'Distribución por línea'!C153+'Distribución por línea'!C220+'Distribución por línea'!C225</f>
         <v>8215.17</v>
       </c>
       <c r="G59" s="11"/>
@@ -5105,8 +5084,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="12">
-        <f>+SALDOS!C230</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C230</f>
       </c>
       <c r="G60" s="11"/>
       <c r="H60" s="1"/>
@@ -5128,7 +5106,7 @@
         <v>547.37</v>
       </c>
       <c r="F61" s="116">
-        <f>+SALDOS!C193</f>
+        <f>+'Distribución por línea'!C193</f>
         <v>547.37</v>
       </c>
       <c r="G61" s="11"/>
@@ -5153,8 +5131,7 @@
       <c r="F62" s="116"/>
       <c r="G62" s="11"/>
       <c r="H62" s="12">
-        <f>+SALDOS!C154</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C154</f>
       </c>
       <c r="I62" s="117"/>
       <c r="J62" s="115"/>
@@ -5174,7 +5151,7 @@
         <v>104.17</v>
       </c>
       <c r="F63" s="116">
-        <f>+SALDOS!C142</f>
+        <f>+'Distribución por línea'!C142</f>
         <v>104.17</v>
       </c>
       <c r="G63" s="11"/>
@@ -5197,12 +5174,12 @@
         <v>62027.53</v>
       </c>
       <c r="F64" s="116">
-        <f>+SALDOS!C118+SALDOS!C182</f>
+        <f>+'Distribución por línea'!C118+'Distribución por línea'!C182</f>
         <v>767.75</v>
       </c>
       <c r="G64" s="11"/>
       <c r="H64" s="12">
-        <f>+SALDOS!C163</f>
+        <f>+'Distribución por línea'!C163</f>
         <v>61259.78</v>
       </c>
       <c r="I64" s="117"/>
@@ -5225,7 +5202,7 @@
       <c r="F65" s="116"/>
       <c r="G65" s="11"/>
       <c r="H65" s="12">
-        <f>+SALDOS!C140</f>
+        <f>+'Distribución por línea'!C140</f>
         <v>71.64</v>
       </c>
       <c r="I65" s="117"/>
@@ -5246,8 +5223,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="116">
-        <f>+SALDOS!C206</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C206</f>
       </c>
       <c r="G66" s="11"/>
       <c r="H66" s="12"/>
@@ -5271,8 +5247,7 @@
       <c r="F67" s="116"/>
       <c r="G67" s="11"/>
       <c r="H67" s="12">
-        <f>+SALDOS!C166</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C166</f>
       </c>
       <c r="I67" s="117"/>
       <c r="J67" s="115"/>
@@ -5292,7 +5267,7 @@
         <v>1487.34</v>
       </c>
       <c r="F68" s="116">
-        <f>+SALDOS!C133</f>
+        <f>+'Distribución por línea'!C133</f>
         <v>1487.34</v>
       </c>
       <c r="G68" s="11"/>
@@ -5317,8 +5292,7 @@
       <c r="F69" s="116"/>
       <c r="G69" s="11"/>
       <c r="H69" s="12">
-        <f>+SALDOS!C179</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C179</f>
       </c>
       <c r="I69" s="117"/>
       <c r="J69" s="115"/>
@@ -5338,13 +5312,11 @@
         <v>0</v>
       </c>
       <c r="F70" s="116">
-        <f>+SALDOS!C224</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C224</f>
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="12">
-        <f>+SALDOS!C181</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C181</f>
       </c>
       <c r="I70" s="117"/>
       <c r="J70" s="115"/>
@@ -5366,8 +5338,7 @@
       <c r="F71" s="116"/>
       <c r="G71" s="11"/>
       <c r="H71" s="12">
-        <f>+SALDOS!C209</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C209</f>
       </c>
       <c r="I71" s="117"/>
       <c r="J71" s="115"/>
@@ -5387,8 +5358,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="116">
-        <f>+SALDOS!C137</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C137</f>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="12"/>
@@ -5410,8 +5380,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="116">
-        <f>+SALDOS!C213</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C213</f>
       </c>
       <c r="G73" s="11"/>
       <c r="H73" s="12"/>
@@ -5433,7 +5402,7 @@
         <v>490.88</v>
       </c>
       <c r="F74" s="11">
-        <f>+SALDOS!C130</f>
+        <f>+'Distribución por línea'!C130</f>
         <v>490.88</v>
       </c>
       <c r="G74" s="11"/>
@@ -5456,7 +5425,7 @@
         <v>2845.01</v>
       </c>
       <c r="F75" s="12">
-        <f>+SALDOS!C207</f>
+        <f>+'Distribución por línea'!C207</f>
         <v>2845.01</v>
       </c>
       <c r="G75" s="11"/>
@@ -5479,8 +5448,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="11">
-        <f>+SALDOS!C129</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C129</f>
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="12"/>
@@ -5502,7 +5470,7 @@
         <v>13077.95</v>
       </c>
       <c r="F77" s="12">
-        <f>+SALDOS!C194</f>
+        <f>+'Distribución por línea'!C194</f>
         <v>13077.95</v>
       </c>
       <c r="G77" s="11"/>
@@ -5525,8 +5493,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="12">
-        <f>+SALDOS!C214</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C214</f>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="1"/>
@@ -5550,7 +5517,7 @@
       <c r="F79" s="12"/>
       <c r="G79" s="11"/>
       <c r="H79" s="1">
-        <f>+SALDOS!C212</f>
+        <f>+'Distribución por línea'!C212</f>
         <v>2925.36</v>
       </c>
       <c r="I79" s="117"/>
@@ -5573,8 +5540,7 @@
       <c r="F80" s="116"/>
       <c r="G80" s="11"/>
       <c r="H80" s="12">
-        <f>+SALDOS!C162</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C162</f>
       </c>
       <c r="I80" s="117"/>
       <c r="J80" s="115"/>
@@ -5596,8 +5562,7 @@
       <c r="F81" s="116"/>
       <c r="G81" s="11"/>
       <c r="H81" s="12">
-        <f>+SALDOS!C210</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C210</f>
       </c>
       <c r="I81" s="117"/>
       <c r="J81" s="115"/>
@@ -5617,12 +5582,12 @@
         <v>301316.8</v>
       </c>
       <c r="F82" s="116">
-        <f>+SALDOS!C116</f>
+        <f>+'Distribución por línea'!C116</f>
         <v>106476.09</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="12">
-        <f>+SALDOS!C185</f>
+        <f>+'Distribución por línea'!C185</f>
         <v>194840.71</v>
       </c>
       <c r="I82" s="117"/>
@@ -5645,7 +5610,7 @@
       <c r="F83" s="116"/>
       <c r="G83" s="11"/>
       <c r="H83" s="12">
-        <f>+SALDOS!C201+SALDOS!C150+SALDOS!C125+SALDOS!C191</f>
+        <f>+'Distribución por línea'!C201+'Distribución por línea'!C150+'Distribución por línea'!C125+'Distribución por línea'!C191</f>
         <v>2468.76</v>
       </c>
       <c r="I83" s="117"/>
@@ -5668,8 +5633,7 @@
       <c r="F84" s="116"/>
       <c r="G84" s="11"/>
       <c r="H84" s="12">
-        <f>+SALDOS!C167+SALDOS!C108</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C167+'Distribución por línea'!C108</f>
       </c>
       <c r="I84" s="117"/>
       <c r="J84" s="115"/>
@@ -5689,8 +5653,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="116">
-        <f>+SALDOS!C145</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C145</f>
       </c>
       <c r="G85" s="11"/>
       <c r="H85" s="12"/>
@@ -5712,8 +5675,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="116">
-        <f>+SALDOS!C177</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C177</f>
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="12"/>
@@ -5735,8 +5697,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="116">
-        <f>+SALDOS!C141</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C141</f>
       </c>
       <c r="G87" s="11"/>
       <c r="H87" s="12"/>
@@ -5758,8 +5719,7 @@
         <v>0</v>
       </c>
       <c r="F88" s="11">
-        <f>+SALDOS!C119</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C119</f>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="12"/>
@@ -5783,8 +5743,7 @@
       <c r="F89" s="11"/>
       <c r="G89" s="11"/>
       <c r="H89" s="12">
-        <f>+SALDOS!C190</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C190</f>
       </c>
       <c r="I89" s="117"/>
       <c r="J89" s="115"/>
@@ -5804,7 +5763,7 @@
         <v>69.84</v>
       </c>
       <c r="F90" s="11">
-        <f>+SALDOS!C197</f>
+        <f>+'Distribución por línea'!C197</f>
         <v>69.84</v>
       </c>
       <c r="G90" s="11"/>
@@ -5829,7 +5788,7 @@
       <c r="F91" s="11"/>
       <c r="G91" s="11"/>
       <c r="H91" s="12">
-        <f>+SALDOS!C211</f>
+        <f>+'Distribución por línea'!C211</f>
         <v>156.87</v>
       </c>
       <c r="I91" s="117"/>
@@ -5850,7 +5809,7 @@
         <v>4965.52</v>
       </c>
       <c r="F92" s="11">
-        <f>+SALDOS!C232</f>
+        <f>+'Distribución por línea'!C232</f>
         <v>4965.52</v>
       </c>
       <c r="G92" s="11"/>
@@ -5873,8 +5832,7 @@
         <v>0</v>
       </c>
       <c r="F93" s="11">
-        <f>+SALDOS!C126</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C126</f>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="12"/>
@@ -5896,7 +5854,7 @@
         <v>651.34</v>
       </c>
       <c r="F94" s="11">
-        <f>+SALDOS!C215</f>
+        <f>+'Distribución por línea'!C215</f>
         <v>651.34</v>
       </c>
       <c r="G94" s="11"/>
@@ -5919,7 +5877,7 @@
         <v>-3057.96</v>
       </c>
       <c r="F95" s="116">
-        <f>+SALDOS!C217</f>
+        <f>+'Distribución por línea'!C217</f>
         <v>-3057.96</v>
       </c>
       <c r="G95" s="11"/>
@@ -5944,8 +5902,7 @@
       <c r="F96" s="116"/>
       <c r="G96" s="11"/>
       <c r="H96" s="120">
-        <f>+SALDOS!C221</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C221</f>
       </c>
       <c r="I96" s="117"/>
       <c r="J96" s="115"/>
@@ -5967,8 +5924,7 @@
       <c r="F97" s="116"/>
       <c r="G97" s="116"/>
       <c r="H97" s="120">
-        <f>+SALDOS!C219</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C219</f>
       </c>
       <c r="I97" s="117"/>
       <c r="J97" s="115"/>
@@ -5990,8 +5946,7 @@
       <c r="F98" s="116"/>
       <c r="G98" s="116"/>
       <c r="H98" s="120">
-        <f>+SALDOS!C226</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C226</f>
       </c>
       <c r="I98" s="117"/>
       <c r="J98" s="115"/>
@@ -6013,8 +5968,7 @@
       <c r="F99" s="116"/>
       <c r="G99" s="116"/>
       <c r="H99" s="120">
-        <f>+SALDOS!C227</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C227</f>
       </c>
       <c r="I99" s="117"/>
       <c r="J99" s="115"/>
@@ -6036,8 +5990,7 @@
       <c r="F100" s="116"/>
       <c r="G100" s="116"/>
       <c r="H100" s="120">
-        <f>+SALDOS!C228</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C228</f>
       </c>
       <c r="I100" s="117"/>
       <c r="J100" s="115"/>
@@ -6059,8 +6012,7 @@
       <c r="F101" s="116"/>
       <c r="G101" s="116"/>
       <c r="H101" s="120">
-        <f>+SALDOS!C231</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C231</f>
       </c>
       <c r="I101" s="117"/>
       <c r="J101" s="115"/>
@@ -6315,8 +6267,7 @@
         <v>296</v>
       </c>
       <c r="C3" s="139">
-        <f>IFERROR(VLOOKUP(B3,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B3,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D3" s="140">
         <v>2677221.3</v>
@@ -6337,7 +6288,7 @@
         <v>297</v>
       </c>
       <c r="C4" s="139">
-        <f>IFERROR(VLOOKUP(B4,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B4,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>5746.23</v>
       </c>
       <c r="D4" s="142"/>
@@ -6354,7 +6305,7 @@
         <v>298</v>
       </c>
       <c r="C5" s="139">
-        <f>IFERROR(VLOOKUP(B5,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B5,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>7239.24</v>
       </c>
       <c r="D5" s="65"/>
@@ -6371,7 +6322,7 @@
         <v>299</v>
       </c>
       <c r="C6" s="139">
-        <f>IFERROR(VLOOKUP(B6,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B6,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>-15.710000000018</v>
       </c>
       <c r="D6" s="65"/>
@@ -6388,7 +6339,7 @@
         <v>300</v>
       </c>
       <c r="C7" s="139">
-        <f>IFERROR(VLOOKUP(B7,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B7,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>981.500000000146</v>
       </c>
       <c r="D7" s="65"/>
@@ -6402,12 +6353,11 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="138"/>
       <c r="B8" s="144" t="str">
-        <f>+Hoja1!A11</f>
+        <f>+'Balance de sumas y saldos'!A11</f>
         <v>111020002 - Banco Macro Cta. Especial en pesos</v>
       </c>
       <c r="C8" s="139">
-        <f>IFERROR(VLOOKUP(B8,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B8,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="143"/>
@@ -6423,7 +6373,7 @@
         <v>301</v>
       </c>
       <c r="C9" s="139">
-        <f>IFERROR(VLOOKUP(B9,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B9,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>2.66999999999998</v>
       </c>
       <c r="D9" s="65"/>
@@ -6440,8 +6390,7 @@
         <v>302</v>
       </c>
       <c r="C10" s="139">
-        <f>IFERROR(VLOOKUP(B10,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B10,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="105"/>
@@ -6457,8 +6406,7 @@
         <v>303</v>
       </c>
       <c r="C11" s="139">
-        <f>IFERROR(VLOOKUP(B11,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B11,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D11" s="142"/>
       <c r="E11" s="135"/>
@@ -6474,8 +6422,7 @@
         <v>304</v>
       </c>
       <c r="C12" s="139">
-        <f>IFERROR(VLOOKUP(B12,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B12,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D12" s="142"/>
       <c r="E12" s="135"/>
@@ -6491,7 +6438,7 @@
         <v>305</v>
       </c>
       <c r="C13" s="139">
-        <f>IFERROR(VLOOKUP(B13,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B13,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>1132355.33</v>
       </c>
       <c r="D13" s="146"/>
@@ -6508,7 +6455,7 @@
         <v>306</v>
       </c>
       <c r="C14" s="139">
-        <f>IFERROR(VLOOKUP(B14,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B14,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>-1.77635683940025e-15</v>
       </c>
       <c r="D14" s="65"/>
@@ -6525,7 +6472,7 @@
         <v>307</v>
       </c>
       <c r="C15" s="139">
-        <f>IFERROR(VLOOKUP(B15,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B15,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>-8.88178419700125e-16</v>
       </c>
       <c r="D15" s="142"/>
@@ -6542,7 +6489,7 @@
         <v>308</v>
       </c>
       <c r="C16" s="139">
-        <f>IFERROR(VLOOKUP(B16,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B16,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>5340.7</v>
       </c>
       <c r="D16" s="65"/>
@@ -6559,7 +6506,7 @@
         <v>309</v>
       </c>
       <c r="C17" s="139">
-        <f>IFERROR(VLOOKUP(B17,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B17,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>35314.56</v>
       </c>
       <c r="D17" s="146"/>
@@ -6576,7 +6523,7 @@
         <v>310</v>
       </c>
       <c r="C18" s="139">
-        <f>IFERROR(VLOOKUP(B18,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B18,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>358.96</v>
       </c>
       <c r="D18" s="146"/>
@@ -6593,8 +6540,7 @@
         <v>311</v>
       </c>
       <c r="C19" s="139">
-        <f>IFERROR(VLOOKUP(B19,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B19,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D19" s="142"/>
       <c r="E19" s="135"/>
@@ -6610,7 +6556,7 @@
         <v>312</v>
       </c>
       <c r="C20" s="139">
-        <f>IFERROR(VLOOKUP(B20,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B20,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>165.44</v>
       </c>
       <c r="D20" s="65"/>
@@ -6627,7 +6573,7 @@
         <v>313</v>
       </c>
       <c r="C21" s="139">
-        <f>IFERROR(VLOOKUP(B21,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B21,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>138.22</v>
       </c>
       <c r="D21" s="65"/>
@@ -6644,7 +6590,7 @@
         <v>314</v>
       </c>
       <c r="C22" s="139">
-        <f>IFERROR(VLOOKUP(B22,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B22,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>1214719.33</v>
       </c>
       <c r="D22" s="65"/>
@@ -6661,8 +6607,7 @@
         <v>315</v>
       </c>
       <c r="C23" s="139">
-        <f>IFERROR(VLOOKUP(B23,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B23,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D23" s="142"/>
       <c r="E23" s="135"/>
@@ -6678,7 +6623,7 @@
         <v>316</v>
       </c>
       <c r="C24" s="139">
-        <f>IFERROR(VLOOKUP(B24,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B24,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>17670.09</v>
       </c>
       <c r="D24" s="142"/>
@@ -6695,8 +6640,7 @@
         <v>317</v>
       </c>
       <c r="C25" s="139">
-        <f>IFERROR(VLOOKUP(B25,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B25,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D25" s="142"/>
       <c r="E25" s="135"/>
@@ -6712,7 +6656,7 @@
         <v>318</v>
       </c>
       <c r="C26" s="139">
-        <f>IFERROR(VLOOKUP(B26,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B26,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>65129.21</v>
       </c>
       <c r="D26" s="65"/>
@@ -6729,7 +6673,7 @@
         <v>319</v>
       </c>
       <c r="C27" s="139">
-        <f>IFERROR(VLOOKUP(B27,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B27,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>0.62</v>
       </c>
       <c r="D27" s="65"/>
@@ -6746,7 +6690,7 @@
         <v>320</v>
       </c>
       <c r="C28" s="139">
-        <f>IFERROR(VLOOKUP(B28,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B28,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>4529.05</v>
       </c>
       <c r="D28" s="65"/>
@@ -6763,8 +6707,7 @@
         <v>321</v>
       </c>
       <c r="C29" s="139">
-        <f>IFERROR(VLOOKUP(B29,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B29,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="65"/>
@@ -6780,8 +6723,7 @@
         <v>322</v>
       </c>
       <c r="C30" s="139">
-        <f>IFERROR(VLOOKUP(B30,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B30,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D30" s="137"/>
       <c r="E30" s="135"/>
@@ -6797,8 +6739,7 @@
         <v>323</v>
       </c>
       <c r="C31" s="139">
-        <f>IFERROR(VLOOKUP(B31,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B31,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D31" s="142"/>
       <c r="E31" s="135"/>
@@ -6814,8 +6755,7 @@
         <v>324</v>
       </c>
       <c r="C32" s="139">
-        <f>IFERROR(VLOOKUP(B32,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B32,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D32" s="142"/>
       <c r="E32" s="135"/>
@@ -6831,8 +6771,7 @@
         <v>325</v>
       </c>
       <c r="C33" s="139">
-        <f>IFERROR(VLOOKUP(B33,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B33,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D33" s="142"/>
       <c r="E33" s="135"/>
@@ -6848,7 +6787,7 @@
         <v>326</v>
       </c>
       <c r="C34" s="139">
-        <f>IFERROR(VLOOKUP(B34,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B34,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>11810.75</v>
       </c>
       <c r="D34" s="65"/>
@@ -6865,7 +6804,7 @@
         <v>327</v>
       </c>
       <c r="C35" s="139">
-        <f>IFERROR(VLOOKUP(B35,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B35,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>219.280000000001</v>
       </c>
       <c r="D35" s="65"/>
@@ -6882,8 +6821,7 @@
         <v>328</v>
       </c>
       <c r="C36" s="139">
-        <f>IFERROR(VLOOKUP(B36,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B36,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="135"/>
@@ -6899,7 +6837,7 @@
         <v>329</v>
       </c>
       <c r="C37" s="139">
-        <f>IFERROR(VLOOKUP(B37,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B37,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>104684</v>
       </c>
       <c r="D37" s="148"/>
@@ -6916,7 +6854,7 @@
         <v>330</v>
       </c>
       <c r="C38" s="139">
-        <f>IFERROR(VLOOKUP(B38,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B38,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>73.46</v>
       </c>
       <c r="D38" s="65"/>
@@ -6933,8 +6871,7 @@
         <v>331</v>
       </c>
       <c r="C39" s="137">
-        <f>IFERROR(VLOOKUP(B39,Hoja1!A:D,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B39,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
       </c>
       <c r="D39" s="142"/>
       <c r="E39" s="135"/>
@@ -6950,7 +6887,7 @@
         <v>332</v>
       </c>
       <c r="C40" s="137">
-        <f>IFERROR(VLOOKUP(B40,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B40,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>130976.14</v>
       </c>
       <c r="D40" s="142"/>
@@ -6973,7 +6910,7 @@
         <v>333</v>
       </c>
       <c r="C41" s="137">
-        <f>IFERROR(VLOOKUP(B41,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B41,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>58450.05</v>
       </c>
       <c r="D41" s="142"/>
@@ -6993,7 +6930,7 @@
         <v>334</v>
       </c>
       <c r="C42" s="137">
-        <f>IFERROR(VLOOKUP(B42,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B42,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>33289.65</v>
       </c>
       <c r="D42" s="129"/>
@@ -7010,7 +6947,7 @@
         <v>335</v>
       </c>
       <c r="C43" s="137">
-        <f>IFERROR(VLOOKUP(B43,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B43,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>78372.31</v>
       </c>
       <c r="D43" s="142"/>
@@ -7027,7 +6964,7 @@
         <v>336</v>
       </c>
       <c r="C44" s="137">
-        <f>IFERROR(VLOOKUP(B44,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B44,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>133453.72</v>
       </c>
       <c r="D44" s="142"/>
@@ -7044,7 +6981,7 @@
         <v>337</v>
       </c>
       <c r="C45" s="150">
-        <f>IFERROR(VLOOKUP(B45,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B45,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>-110762.6</v>
       </c>
       <c r="D45" s="142">
@@ -7066,7 +7003,7 @@
         <v>338</v>
       </c>
       <c r="C46" s="150">
-        <f>IFERROR(VLOOKUP(B46,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B46,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>-55642.59</v>
       </c>
       <c r="D46" s="142">
@@ -7088,7 +7025,7 @@
         <v>339</v>
       </c>
       <c r="C47" s="150">
-        <f>IFERROR(VLOOKUP(B47,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B47,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>-23489.12</v>
       </c>
       <c r="D47" s="142">
@@ -7110,7 +7047,7 @@
         <v>340</v>
       </c>
       <c r="C48" s="137">
-        <f>IFERROR(VLOOKUP(B48,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B48,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>279626.68</v>
       </c>
       <c r="D48" s="142"/>
@@ -7127,7 +7064,7 @@
         <v>341</v>
       </c>
       <c r="C49" s="150">
-        <f>IFERROR(VLOOKUP(B49,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B49,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>-67464.69</v>
       </c>
       <c r="D49" s="142">
@@ -7149,7 +7086,7 @@
         <v>342</v>
       </c>
       <c r="C50" s="150">
-        <f>IFERROR(VLOOKUP(B50,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B50,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>-133453.72</v>
       </c>
       <c r="D50" s="142">
@@ -7171,7 +7108,7 @@
         <v>343</v>
       </c>
       <c r="C51" s="150">
-        <f>IFERROR(VLOOKUP(B51,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B51,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>-266119.74</v>
       </c>
       <c r="D51" s="142">
@@ -7193,7 +7130,7 @@
         <v>344</v>
       </c>
       <c r="C52" s="137">
-        <f>IFERROR(VLOOKUP(B52,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B52,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>136820.25</v>
       </c>
       <c r="D52" s="142"/>
@@ -7210,7 +7147,7 @@
         <v>345</v>
       </c>
       <c r="C53" s="150">
-        <f>IFERROR(VLOOKUP(B53,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B53,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>-127115.9</v>
       </c>
       <c r="D53" s="142">
@@ -7232,7 +7169,7 @@
         <v>346</v>
       </c>
       <c r="C54" s="137">
-        <f>IFERROR(VLOOKUP(B54,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B54,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>11629.81</v>
       </c>
       <c r="D54" s="142"/>
@@ -7249,7 +7186,7 @@
         <v>347</v>
       </c>
       <c r="C55" s="150">
-        <f>IFERROR(VLOOKUP(B55,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B55,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>-5701.57</v>
       </c>
       <c r="D55" s="142">
@@ -7271,7 +7208,7 @@
         <v>348</v>
       </c>
       <c r="C56" s="139">
-        <f>IFERROR(VLOOKUP(B56,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B56,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>165358.57</v>
       </c>
       <c r="D56" s="142"/>
@@ -7290,7 +7227,7 @@
         <v>349</v>
       </c>
       <c r="C57" s="139">
-        <f>IFERROR(VLOOKUP(B57,Hoja1!A:D,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B57,'Balance de sumas y saldos'!A:D,4,FALSE),)</f>
         <v>1063586.36</v>
       </c>
       <c r="D57" s="142"/>
@@ -7350,7 +7287,7 @@
         <v>351</v>
       </c>
       <c r="C61" s="156">
-        <f>+Hoja1!D68</f>
+        <f>+'Balance de sumas y saldos'!D68</f>
         <v>-71988.8751050439</v>
       </c>
       <c r="D61" s="135"/>
@@ -7586,7 +7523,7 @@
         <v>352</v>
       </c>
       <c r="C80" s="157">
-        <f>IFERROR(VLOOKUP(B80,Hoja1!$A$27:$D$444,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B80,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
         <v>-1208275.2</v>
       </c>
       <c r="D80" s="65"/>
@@ -7605,7 +7542,7 @@
         <v>353</v>
       </c>
       <c r="C81" s="157">
-        <f>IFERROR(VLOOKUP(B81,Hoja1!$A$27:$D$444,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B81,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
         <v>-521.21</v>
       </c>
       <c r="D81" s="65"/>
@@ -7624,7 +7561,7 @@
         <v>354</v>
       </c>
       <c r="C82" s="157">
-        <f>IFERROR(VLOOKUP(B82,Hoja1!$A$27:$D$444,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B82,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
         <v>-25741.92</v>
       </c>
       <c r="D82" s="65"/>
@@ -7643,7 +7580,7 @@
         <v>356</v>
       </c>
       <c r="C83" s="157">
-        <f>IFERROR(VLOOKUP(B83,Hoja1!$A$27:$D$444,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B83,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
         <v>-31629.29</v>
       </c>
       <c r="D83" s="65"/>
@@ -7660,8 +7597,7 @@
         <v>357</v>
       </c>
       <c r="C84" s="157">
-        <f>IFERROR(VLOOKUP(B84,Hoja1!$A$27:$D$444,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B84,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
       </c>
       <c r="D84" s="142"/>
       <c r="E84" s="135"/>
@@ -7677,8 +7613,7 @@
         <v>358</v>
       </c>
       <c r="C85" s="157">
-        <f>IFERROR(VLOOKUP(B85,Hoja1!$A$27:$D$444,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B85,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
       </c>
       <c r="D85" s="142"/>
       <c r="E85" s="135"/>
@@ -7696,7 +7631,7 @@
         <v>360</v>
       </c>
       <c r="C86" s="157">
-        <f>IFERROR(VLOOKUP(B86,Hoja1!$A$27:$D$444,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B86,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
         <v>-134391.6</v>
       </c>
       <c r="D86" s="65"/>
@@ -7715,7 +7650,7 @@
         <v>362</v>
       </c>
       <c r="C87" s="157">
-        <f>IFERROR(VLOOKUP(B87,Hoja1!$A$27:$D$444,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B87,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
         <v>-26660.31</v>
       </c>
       <c r="D87" s="146"/>
@@ -7732,8 +7667,7 @@
         <v>363</v>
       </c>
       <c r="C88" s="157">
-        <f>IFERROR(VLOOKUP(B88,Hoja1!$A$27:$D$444,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B88,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
       </c>
       <c r="D88" s="154"/>
       <c r="E88" s="135"/>
@@ -7749,8 +7683,7 @@
         <v>364</v>
       </c>
       <c r="C89" s="157">
-        <f>IFERROR(VLOOKUP(B89,Hoja1!$A$27:$D$444,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B89,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
       </c>
       <c r="D89" s="142"/>
       <c r="E89" s="135"/>
@@ -7766,8 +7699,7 @@
         <v>365</v>
       </c>
       <c r="C90" s="157">
-        <f>IFERROR(VLOOKUP(B90,Hoja1!$A$27:$D$444,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B90,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
       </c>
       <c r="D90" s="142"/>
       <c r="E90" s="135"/>
@@ -7783,8 +7715,7 @@
         <v>366</v>
       </c>
       <c r="C91" s="157">
-        <f>IFERROR(VLOOKUP(B91,Hoja1!$A$27:$D$444,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B91,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
       </c>
       <c r="D91" s="142"/>
       <c r="E91" s="158" t="s">
@@ -7802,8 +7733,7 @@
         <v>367</v>
       </c>
       <c r="C92" s="157">
-        <f>IFERROR(VLOOKUP(B92,Hoja1!$A$27:$D$444,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B92,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
       </c>
       <c r="D92" s="142"/>
       <c r="E92" s="135">
@@ -7825,7 +7755,7 @@
         <v>368</v>
       </c>
       <c r="C93" s="157">
-        <f>IFERROR(VLOOKUP(B93,Hoja1!$A$27:$D$444,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B93,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
         <v>-13.32</v>
       </c>
       <c r="D93" s="142"/>
@@ -7845,8 +7775,7 @@
         <v>369</v>
       </c>
       <c r="C94" s="157">
-        <f>IFERROR(VLOOKUP(B94,Hoja1!$A$27:$D$444,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B94,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
       </c>
       <c r="D94" s="142"/>
       <c r="E94" s="135"/>
@@ -7862,7 +7791,7 @@
         <v>370</v>
       </c>
       <c r="C95" s="157">
-        <f>IFERROR(VLOOKUP(B95,Hoja1!$A$27:$D$444,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B95,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
         <v>-0.900000000000002</v>
       </c>
       <c r="D95" s="142"/>
@@ -7879,7 +7808,7 @@
         <v>371</v>
       </c>
       <c r="C96" s="157">
-        <f>IFERROR(VLOOKUP(B96,Hoja1!$A$27:$D$444,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B96,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
         <v>-3.90798504668055e-14</v>
       </c>
       <c r="D96" s="142"/>
@@ -7934,7 +7863,7 @@
         <v>373</v>
       </c>
       <c r="C100" s="137">
-        <f>IFERROR(VLOOKUP(B100,Hoja1!$A$27:$D$444,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B100,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
         <v>-51718582.9</v>
       </c>
       <c r="D100" s="129"/>
@@ -7953,7 +7882,7 @@
         <v>375</v>
       </c>
       <c r="C101" s="137">
-        <f>IFERROR(VLOOKUP(B101,Hoja1!$A$27:$D$444,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B101,'Balance de sumas y saldos'!$A$27:$D$444,4,FALSE),)</f>
         <v>48116541.3746332</v>
       </c>
       <c r="D101" s="142"/>
@@ -7970,8 +7899,7 @@
         <v>376</v>
       </c>
       <c r="C102" s="137">
-        <f>IFERROR(VLOOKUP(B102,Hoja1!$A$27:$D$438,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B102,'Balance de sumas y saldos'!$A$27:$D$438,4,FALSE),)</f>
       </c>
       <c r="D102" s="142"/>
       <c r="E102" s="135"/>
@@ -7987,8 +7915,7 @@
         <v>73</v>
       </c>
       <c r="C103" s="137">
-        <f>IFERROR(VLOOKUP(B103,Hoja1!$A$27:$D$438,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B103,'Balance de sumas y saldos'!$A$27:$D$438,4,FALSE),)</f>
       </c>
       <c r="D103" s="142"/>
       <c r="E103" s="135"/>
@@ -8028,8 +7955,7 @@
         <v>377</v>
       </c>
       <c r="C106" s="137">
-        <f>IFERROR(VLOOKUP(B106,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B106,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D106" s="146"/>
       <c r="E106" s="135"/>
@@ -8045,8 +7971,7 @@
         <v>378</v>
       </c>
       <c r="C107" s="137">
-        <f>IFERROR(VLOOKUP(B107,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B107,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D107" s="142"/>
       <c r="E107" s="135"/>
@@ -8062,8 +7987,7 @@
         <v>379</v>
       </c>
       <c r="C108" s="137">
-        <f>IFERROR(VLOOKUP(B108,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B108,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D108" s="142"/>
       <c r="E108" s="135"/>
@@ -8079,8 +8003,7 @@
         <v>380</v>
       </c>
       <c r="C109" s="137">
-        <f>IFERROR(VLOOKUP(B109,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B109,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D109" s="142"/>
       <c r="E109" s="135"/>
@@ -8096,8 +8019,7 @@
         <v>381</v>
       </c>
       <c r="C110" s="137">
-        <f>IFERROR(VLOOKUP(B110,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B110,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D110" s="142"/>
       <c r="E110" s="135"/>
@@ -8113,8 +8035,7 @@
         <v>382</v>
       </c>
       <c r="C111" s="137">
-        <f>IFERROR(VLOOKUP(B111,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B111,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D111" s="142"/>
       <c r="E111" s="135"/>
@@ -8130,8 +8051,7 @@
         <v>383</v>
       </c>
       <c r="C112" s="137">
-        <f>IFERROR(VLOOKUP(B112,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B112,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D112" s="142"/>
       <c r="E112" s="135"/>
@@ -8149,8 +8069,7 @@
         <v>384</v>
       </c>
       <c r="C113" s="137">
-        <f>IFERROR(VLOOKUP(B113,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B113,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D113" s="142"/>
       <c r="E113" s="135"/>
@@ -8166,7 +8085,7 @@
         <v>385</v>
       </c>
       <c r="C114" s="137">
-        <f>IFERROR(VLOOKUP(B114,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B114,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>119655.77</v>
       </c>
       <c r="D114" s="142"/>
@@ -8183,8 +8102,7 @@
         <v>386</v>
       </c>
       <c r="C115" s="137">
-        <f>IFERROR(VLOOKUP(B115,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B115,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D115" s="142"/>
       <c r="E115" s="135"/>
@@ -8200,7 +8118,7 @@
         <v>387</v>
       </c>
       <c r="C116" s="137">
-        <f>IFERROR(VLOOKUP(B116,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B116,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>106476.09</v>
       </c>
       <c r="D116" s="142"/>
@@ -8217,7 +8135,7 @@
         <v>388</v>
       </c>
       <c r="C117" s="137">
-        <f>IFERROR(VLOOKUP(B117,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B117,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>10000.93</v>
       </c>
       <c r="D117" s="142"/>
@@ -8234,7 +8152,7 @@
         <v>389</v>
       </c>
       <c r="C118" s="137">
-        <f>IFERROR(VLOOKUP(B118,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B118,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>767.75</v>
       </c>
       <c r="D118" s="142"/>
@@ -8251,8 +8169,7 @@
         <v>390</v>
       </c>
       <c r="C119" s="137">
-        <f>IFERROR(VLOOKUP(B119,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B119,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D119" s="142"/>
       <c r="E119" s="135"/>
@@ -8268,7 +8185,7 @@
         <v>391</v>
       </c>
       <c r="C120" s="137">
-        <f>IFERROR(VLOOKUP(B120,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B120,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>21.03</v>
       </c>
       <c r="D120" s="142"/>
@@ -8285,7 +8202,7 @@
         <v>392</v>
       </c>
       <c r="C121" s="137">
-        <f>IFERROR(VLOOKUP(B121,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B121,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>2811.7</v>
       </c>
       <c r="D121" s="142"/>
@@ -8302,8 +8219,7 @@
         <v>393</v>
       </c>
       <c r="C122" s="137">
-        <f>IFERROR(VLOOKUP(B122,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B122,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D122" s="142"/>
       <c r="E122" s="135"/>
@@ -8319,8 +8235,7 @@
         <v>394</v>
       </c>
       <c r="C123" s="137">
-        <f>IFERROR(VLOOKUP(B123,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B123,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D123" s="142"/>
       <c r="E123" s="135"/>
@@ -8336,7 +8251,7 @@
         <v>395</v>
       </c>
       <c r="C124" s="137">
-        <f>IFERROR(VLOOKUP(B124,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B124,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>7383.83</v>
       </c>
       <c r="D124" s="142"/>
@@ -8353,8 +8268,7 @@
         <v>396</v>
       </c>
       <c r="C125" s="137">
-        <f>IFERROR(VLOOKUP(B125,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B125,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D125" s="142"/>
       <c r="E125" s="135"/>
@@ -8370,8 +8284,7 @@
         <v>397</v>
       </c>
       <c r="C126" s="137">
-        <f>IFERROR(VLOOKUP(B126,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B126,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D126" s="142"/>
       <c r="E126" s="135"/>
@@ -8387,8 +8300,7 @@
         <v>398</v>
       </c>
       <c r="C127" s="137">
-        <f>IFERROR(VLOOKUP(B127,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B127,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D127" s="142"/>
       <c r="E127" s="135"/>
@@ -8404,7 +8316,7 @@
         <v>399</v>
       </c>
       <c r="C128" s="137">
-        <f>IFERROR(VLOOKUP(B128,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B128,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>12378.87</v>
       </c>
       <c r="D128" s="142">
@@ -8423,8 +8335,7 @@
         <v>400</v>
       </c>
       <c r="C129" s="137">
-        <f>IFERROR(VLOOKUP(B129,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B129,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D129" s="142"/>
       <c r="E129" s="135"/>
@@ -8440,7 +8351,7 @@
         <v>401</v>
       </c>
       <c r="C130" s="137">
-        <f>IFERROR(VLOOKUP(B130,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B130,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>490.88</v>
       </c>
       <c r="D130" s="142"/>
@@ -8457,7 +8368,7 @@
         <v>402</v>
       </c>
       <c r="C131" s="137">
-        <f>IFERROR(VLOOKUP(B131,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B131,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>201.42</v>
       </c>
       <c r="D131" s="142"/>
@@ -8474,7 +8385,7 @@
         <v>403</v>
       </c>
       <c r="C132" s="137">
-        <f>IFERROR(VLOOKUP(B132,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B132,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>3543.26</v>
       </c>
       <c r="D132" s="146"/>
@@ -8491,7 +8402,7 @@
         <v>404</v>
       </c>
       <c r="C133" s="137">
-        <f>IFERROR(VLOOKUP(B133,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B133,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>1487.34</v>
       </c>
       <c r="D133" s="142"/>
@@ -8508,8 +8419,7 @@
         <v>405</v>
       </c>
       <c r="C134" s="137">
-        <f>IFERROR(VLOOKUP(B134,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B134,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D134" s="142"/>
       <c r="E134" s="135"/>
@@ -8525,8 +8435,7 @@
         <v>406</v>
       </c>
       <c r="C135" s="137">
-        <f>IFERROR(VLOOKUP(B135,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B135,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D135" s="142"/>
       <c r="E135" s="135"/>
@@ -8542,8 +8451,7 @@
         <v>407</v>
       </c>
       <c r="C136" s="137">
-        <f>IFERROR(VLOOKUP(B136,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B136,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D136" s="142"/>
       <c r="E136" s="135"/>
@@ -8559,8 +8467,7 @@
         <v>408</v>
       </c>
       <c r="C137" s="137">
-        <f>IFERROR(VLOOKUP(B137,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B137,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D137" s="142"/>
       <c r="E137" s="135"/>
@@ -8576,8 +8483,7 @@
         <v>409</v>
       </c>
       <c r="C138" s="137">
-        <f>IFERROR(VLOOKUP(B138,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B138,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D138" s="142"/>
       <c r="E138" s="135"/>
@@ -8593,8 +8499,7 @@
         <v>410</v>
       </c>
       <c r="C139" s="137">
-        <f>IFERROR(VLOOKUP(B139,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B139,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D139" s="142"/>
       <c r="E139" s="135"/>
@@ -8610,7 +8515,7 @@
         <v>411</v>
       </c>
       <c r="C140" s="137">
-        <f>IFERROR(VLOOKUP(B140,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B140,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>71.64</v>
       </c>
       <c r="D140" s="65"/>
@@ -8627,8 +8532,7 @@
         <v>412</v>
       </c>
       <c r="C141" s="137">
-        <f>IFERROR(VLOOKUP(B141,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B141,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D141" s="142"/>
       <c r="E141" s="135"/>
@@ -8644,7 +8548,7 @@
         <v>413</v>
       </c>
       <c r="C142" s="137">
-        <f>IFERROR(VLOOKUP(B142,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B142,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>104.17</v>
       </c>
       <c r="D142" s="65"/>
@@ -8661,8 +8565,7 @@
         <v>414</v>
       </c>
       <c r="C143" s="137">
-        <f>IFERROR(VLOOKUP(B143,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B143,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D143" s="142"/>
       <c r="E143" s="135"/>
@@ -8678,8 +8581,7 @@
         <v>415</v>
       </c>
       <c r="C144" s="137">
-        <f>IFERROR(VLOOKUP(B144,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B144,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D144" s="142"/>
       <c r="E144" s="135"/>
@@ -8695,8 +8597,7 @@
         <v>416</v>
       </c>
       <c r="C145" s="137">
-        <f>IFERROR(VLOOKUP(B145,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B145,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D145" s="142"/>
       <c r="E145" s="135"/>
@@ -8712,7 +8613,7 @@
         <v>417</v>
       </c>
       <c r="C146" s="137">
-        <f>IFERROR(VLOOKUP(B146,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B146,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>6613.93</v>
       </c>
       <c r="D146" s="65"/>
@@ -8729,7 +8630,7 @@
         <v>418</v>
       </c>
       <c r="C147" s="137">
-        <f>IFERROR(VLOOKUP(B147,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B147,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>15857.28</v>
       </c>
       <c r="D147" s="65"/>
@@ -8746,8 +8647,7 @@
         <v>419</v>
       </c>
       <c r="C148" s="137">
-        <f>IFERROR(VLOOKUP(B148,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B148,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D148" s="142"/>
       <c r="E148" s="135"/>
@@ -8763,7 +8663,7 @@
         <v>420</v>
       </c>
       <c r="C149" s="137">
-        <f>IFERROR(VLOOKUP(B149,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B149,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>46243.8675605284</v>
       </c>
       <c r="D149" s="65"/>
@@ -8780,8 +8680,7 @@
         <v>421</v>
       </c>
       <c r="C150" s="137">
-        <f>IFERROR(VLOOKUP(B150,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B150,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D150" s="142"/>
       <c r="E150" s="135"/>
@@ -8797,8 +8696,7 @@
         <v>422</v>
       </c>
       <c r="C151" s="137">
-        <f>IFERROR(VLOOKUP(B151,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B151,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D151" s="142"/>
       <c r="E151" s="135"/>
@@ -8814,8 +8712,7 @@
         <v>423</v>
       </c>
       <c r="C152" s="137">
-        <f>IFERROR(VLOOKUP(B152,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B152,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D152" s="142"/>
       <c r="E152" s="135"/>
@@ -8831,7 +8728,7 @@
         <v>424</v>
       </c>
       <c r="C153" s="137">
-        <f>IFERROR(VLOOKUP(B153,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B153,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>8215.17</v>
       </c>
       <c r="D153" s="142"/>
@@ -8848,8 +8745,7 @@
         <v>425</v>
       </c>
       <c r="C154" s="137">
-        <f>IFERROR(VLOOKUP(B154,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B154,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D154" s="142"/>
       <c r="E154" s="135"/>
@@ -8865,7 +8761,7 @@
         <v>426</v>
       </c>
       <c r="C155" s="137">
-        <f>IFERROR(VLOOKUP(B155,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B155,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>603.68</v>
       </c>
       <c r="D155" s="142"/>
@@ -8882,7 +8778,7 @@
         <v>427</v>
       </c>
       <c r="C156" s="137">
-        <f>IFERROR(VLOOKUP(B156,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B156,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>130.73</v>
       </c>
       <c r="D156" s="142"/>
@@ -8899,8 +8795,7 @@
         <v>428</v>
       </c>
       <c r="C157" s="137">
-        <f>IFERROR(VLOOKUP(B157,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B157,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D157" s="142"/>
       <c r="E157" s="135"/>
@@ -8916,8 +8811,7 @@
         <v>429</v>
       </c>
       <c r="C158" s="137">
-        <f>IFERROR(VLOOKUP(B158,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B158,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D158" s="142"/>
       <c r="E158" s="135"/>
@@ -8933,8 +8827,7 @@
         <v>430</v>
       </c>
       <c r="C159" s="137">
-        <f>IFERROR(VLOOKUP(B159,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B159,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D159" s="142"/>
       <c r="E159" s="135"/>
@@ -8950,8 +8843,7 @@
         <v>431</v>
       </c>
       <c r="C160" s="137">
-        <f>IFERROR(VLOOKUP(B160,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B160,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D160" s="142"/>
       <c r="E160" s="135"/>
@@ -8967,7 +8859,7 @@
         <v>432</v>
       </c>
       <c r="C161" s="137">
-        <f>IFERROR(VLOOKUP(B161,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B161,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>13.29</v>
       </c>
       <c r="D161" s="142"/>
@@ -8984,8 +8876,7 @@
         <v>433</v>
       </c>
       <c r="C162" s="137">
-        <f>IFERROR(VLOOKUP(B162,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B162,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D162" s="65"/>
       <c r="E162" s="135"/>
@@ -9001,7 +8892,7 @@
         <v>434</v>
       </c>
       <c r="C163" s="137">
-        <f>IFERROR(VLOOKUP(B163,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B163,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>61259.78</v>
       </c>
       <c r="D163" s="142"/>
@@ -9018,7 +8909,7 @@
         <v>435</v>
       </c>
       <c r="C164" s="137">
-        <f>IFERROR(VLOOKUP(B164,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B164,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>36709.74</v>
       </c>
       <c r="D164" s="142"/>
@@ -9035,7 +8926,7 @@
         <v>436</v>
       </c>
       <c r="C165" s="137">
-        <f>IFERROR(VLOOKUP(B165,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B165,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>19390</v>
       </c>
       <c r="D165" s="142"/>
@@ -9052,8 +8943,7 @@
         <v>437</v>
       </c>
       <c r="C166" s="137">
-        <f>IFERROR(VLOOKUP(B166,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B166,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D166" s="142"/>
       <c r="E166" s="135"/>
@@ -9069,8 +8959,7 @@
         <v>438</v>
       </c>
       <c r="C167" s="137">
-        <f>IFERROR(VLOOKUP(B167,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B167,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D167" s="142"/>
       <c r="E167" s="135"/>
@@ -9086,7 +8975,7 @@
         <v>439</v>
       </c>
       <c r="C168" s="137">
-        <f>IFERROR(VLOOKUP(B168,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B168,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>5298.39</v>
       </c>
       <c r="D168" s="142"/>
@@ -9103,7 +8992,7 @@
         <v>440</v>
       </c>
       <c r="C169" s="137">
-        <f>IFERROR(VLOOKUP(B169,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B169,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>6051.11</v>
       </c>
       <c r="D169" s="142"/>
@@ -9120,8 +9009,7 @@
         <v>441</v>
       </c>
       <c r="C170" s="137">
-        <f>IFERROR(VLOOKUP(B170,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B170,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D170" s="137"/>
       <c r="E170" s="135"/>
@@ -9137,8 +9025,7 @@
         <v>442</v>
       </c>
       <c r="C171" s="137">
-        <f>IFERROR(VLOOKUP(B171,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B171,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D171" s="137"/>
       <c r="E171" s="135"/>
@@ -9154,8 +9041,7 @@
         <v>443</v>
       </c>
       <c r="C172" s="137">
-        <f>IFERROR(VLOOKUP(B172,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B172,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D172" s="137"/>
       <c r="E172" s="135"/>
@@ -9171,8 +9057,7 @@
         <v>444</v>
       </c>
       <c r="C173" s="137">
-        <f>IFERROR(VLOOKUP(B173,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B173,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D173" s="142"/>
       <c r="E173" s="135"/>
@@ -9188,8 +9073,7 @@
         <v>445</v>
       </c>
       <c r="C174" s="137">
-        <f>IFERROR(VLOOKUP(B174,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B174,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D174" s="137"/>
       <c r="E174" s="135"/>
@@ -9205,7 +9089,7 @@
         <v>446</v>
       </c>
       <c r="C175" s="137">
-        <f>IFERROR(VLOOKUP(B175,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B175,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>185113.95</v>
       </c>
       <c r="D175" s="142"/>
@@ -9222,7 +9106,7 @@
         <v>447</v>
       </c>
       <c r="C176" s="137">
-        <f>IFERROR(VLOOKUP(B176,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B176,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>41896.28</v>
       </c>
       <c r="D176" s="142"/>
@@ -9239,8 +9123,7 @@
         <v>448</v>
       </c>
       <c r="C177" s="137">
-        <f>IFERROR(VLOOKUP(B177,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B177,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D177" s="142"/>
       <c r="E177" s="135"/>
@@ -9256,8 +9139,7 @@
         <v>449</v>
       </c>
       <c r="C178" s="137">
-        <f>IFERROR(VLOOKUP(B178,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B178,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D178" s="142"/>
       <c r="E178" s="135"/>
@@ -9273,8 +9155,7 @@
         <v>450</v>
       </c>
       <c r="C179" s="137">
-        <f>IFERROR(VLOOKUP(B179,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B179,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D179" s="142"/>
       <c r="E179" s="135"/>
@@ -9290,8 +9171,7 @@
         <v>451</v>
       </c>
       <c r="C180" s="137">
-        <f>IFERROR(VLOOKUP(B180,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B180,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D180" s="142"/>
       <c r="E180" s="135"/>
@@ -9307,8 +9187,7 @@
         <v>452</v>
       </c>
       <c r="C181" s="137">
-        <f>IFERROR(VLOOKUP(B181,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B181,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D181" s="129"/>
       <c r="E181" s="129"/>
@@ -9324,8 +9203,7 @@
         <v>453</v>
       </c>
       <c r="C182" s="137">
-        <f>IFERROR(VLOOKUP(B182,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B182,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D182" s="129"/>
       <c r="E182" s="129"/>
@@ -9341,7 +9219,7 @@
         <v>454</v>
       </c>
       <c r="C183" s="137">
-        <f>IFERROR(VLOOKUP(B183,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B183,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>6455.22</v>
       </c>
       <c r="D183" s="129"/>
@@ -9358,7 +9236,7 @@
         <v>455</v>
       </c>
       <c r="C184" s="137">
-        <f>IFERROR(VLOOKUP(B184,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B184,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>4064.29</v>
       </c>
       <c r="D184" s="129"/>
@@ -9375,7 +9253,7 @@
         <v>456</v>
       </c>
       <c r="C185" s="137">
-        <f>IFERROR(VLOOKUP(B185,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B185,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>194840.71</v>
       </c>
       <c r="D185" s="129"/>
@@ -9392,8 +9270,7 @@
         <v>457</v>
       </c>
       <c r="C186" s="137">
-        <f>IFERROR(VLOOKUP(B186,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B186,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D186" s="129"/>
       <c r="E186" s="129"/>
@@ -9409,8 +9286,7 @@
         <v>458</v>
       </c>
       <c r="C187" s="137">
-        <f>IFERROR(VLOOKUP(B187,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B187,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D187" s="129"/>
       <c r="E187" s="129"/>
@@ -9426,7 +9302,7 @@
         <v>459</v>
       </c>
       <c r="C188" s="137">
-        <f>IFERROR(VLOOKUP(B188,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B188,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>346.02</v>
       </c>
       <c r="D188" s="129"/>
@@ -9443,7 +9319,7 @@
         <v>460</v>
       </c>
       <c r="C189" s="137">
-        <f>IFERROR(VLOOKUP(B189,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B189,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>165115.85</v>
       </c>
       <c r="D189" s="129"/>
@@ -9460,8 +9336,7 @@
         <v>461</v>
       </c>
       <c r="C190" s="137">
-        <f>IFERROR(VLOOKUP(B190,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B190,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D190" s="129"/>
       <c r="E190" s="129"/>
@@ -9477,7 +9352,7 @@
         <v>462</v>
       </c>
       <c r="C191" s="137">
-        <f>IFERROR(VLOOKUP(B191,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B191,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>2124.26</v>
       </c>
       <c r="D191" s="129"/>
@@ -9494,7 +9369,7 @@
         <v>463</v>
       </c>
       <c r="C192" s="137">
-        <f>IFERROR(VLOOKUP(B192,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B192,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>36686.71</v>
       </c>
       <c r="D192" s="129"/>
@@ -9511,7 +9386,7 @@
         <v>464</v>
       </c>
       <c r="C193" s="137">
-        <f>IFERROR(VLOOKUP(B193,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B193,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>547.37</v>
       </c>
       <c r="D193" s="65"/>
@@ -9528,7 +9403,7 @@
         <v>465</v>
       </c>
       <c r="C194" s="137">
-        <f>IFERROR(VLOOKUP(B194,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B194,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>13077.95</v>
       </c>
       <c r="D194" s="129"/>
@@ -9545,8 +9420,7 @@
         <v>466</v>
       </c>
       <c r="C195" s="137">
-        <f>IFERROR(VLOOKUP(B195,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B195,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D195" s="129"/>
       <c r="E195" s="129"/>
@@ -9562,8 +9436,7 @@
         <v>467</v>
       </c>
       <c r="C196" s="137">
-        <f>IFERROR(VLOOKUP(B196,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B196,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D196" s="129"/>
       <c r="E196" s="129"/>
@@ -9579,7 +9452,7 @@
         <v>468</v>
       </c>
       <c r="C197" s="137">
-        <f>IFERROR(VLOOKUP(B197,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B197,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>69.84</v>
       </c>
       <c r="D197" s="140"/>
@@ -9596,7 +9469,7 @@
         <v>469</v>
       </c>
       <c r="C198" s="137">
-        <f>IFERROR(VLOOKUP(B198,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B198,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>6055.09</v>
       </c>
       <c r="D198" s="129"/>
@@ -9613,7 +9486,7 @@
         <v>470</v>
       </c>
       <c r="C199" s="137">
-        <f>IFERROR(VLOOKUP(B199,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B199,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>10257.79</v>
       </c>
       <c r="D199" s="105"/>
@@ -9630,8 +9503,7 @@
         <v>471</v>
       </c>
       <c r="C200" s="137">
-        <f>IFERROR(VLOOKUP(B200,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B200,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D200" s="129"/>
       <c r="E200" s="129"/>
@@ -9647,7 +9519,7 @@
         <v>472</v>
       </c>
       <c r="C201" s="137">
-        <f>IFERROR(VLOOKUP(B201,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B201,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>344.5</v>
       </c>
       <c r="D201" s="129"/>
@@ -9664,8 +9536,7 @@
         <v>473</v>
       </c>
       <c r="C202" s="137">
-        <f>IFERROR(VLOOKUP(B202,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B202,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D202" s="105"/>
       <c r="E202" s="129"/>
@@ -9681,7 +9552,7 @@
         <v>474</v>
       </c>
       <c r="C203" s="137">
-        <f>IFERROR(VLOOKUP(B203,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B203,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>10991.7</v>
       </c>
       <c r="D203" s="129"/>
@@ -9698,8 +9569,7 @@
         <v>475</v>
       </c>
       <c r="C204" s="137">
-        <f>IFERROR(VLOOKUP(B204,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B204,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D204" s="129"/>
       <c r="E204" s="129"/>
@@ -9715,8 +9585,7 @@
         <v>476</v>
       </c>
       <c r="C205" s="137">
-        <f>IFERROR(VLOOKUP(B205,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B205,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D205" s="105"/>
       <c r="E205" s="105"/>
@@ -9732,8 +9601,7 @@
         <v>477</v>
       </c>
       <c r="C206" s="137">
-        <f>IFERROR(VLOOKUP(B206,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B206,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D206" s="129"/>
       <c r="E206" s="129"/>
@@ -9749,7 +9617,7 @@
         <v>478</v>
       </c>
       <c r="C207" s="137">
-        <f>IFERROR(VLOOKUP(B207,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B207,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>2845.01</v>
       </c>
       <c r="D207" s="129"/>
@@ -9766,8 +9634,7 @@
         <v>479</v>
       </c>
       <c r="C208" s="137">
-        <f>IFERROR(VLOOKUP(B208,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B208,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D208" s="129"/>
       <c r="E208" s="129"/>
@@ -9783,8 +9650,7 @@
         <v>480</v>
       </c>
       <c r="C209" s="137">
-        <f>IFERROR(VLOOKUP(B209,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B209,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D209" s="129"/>
       <c r="E209" s="129"/>
@@ -9800,8 +9666,7 @@
         <v>481</v>
       </c>
       <c r="C210" s="137">
-        <f>IFERROR(VLOOKUP(B210,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B210,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D210" s="140"/>
       <c r="E210" s="140"/>
@@ -9817,7 +9682,7 @@
         <v>482</v>
       </c>
       <c r="C211" s="137">
-        <f>IFERROR(VLOOKUP(B211,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B211,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>156.87</v>
       </c>
       <c r="D211" s="129"/>
@@ -9834,7 +9699,7 @@
         <v>483</v>
       </c>
       <c r="C212" s="137">
-        <f>IFERROR(VLOOKUP(B212,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B212,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>2925.36</v>
       </c>
       <c r="D212" s="129"/>
@@ -9851,8 +9716,7 @@
         <v>484</v>
       </c>
       <c r="C213" s="137">
-        <f>IFERROR(VLOOKUP(B213,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B213,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D213" s="129"/>
       <c r="E213" s="129"/>
@@ -9868,8 +9732,7 @@
         <v>485</v>
       </c>
       <c r="C214" s="137">
-        <f>IFERROR(VLOOKUP(B214,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B214,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D214" s="129"/>
       <c r="E214" s="129"/>
@@ -9885,7 +9748,7 @@
         <v>486</v>
       </c>
       <c r="C215" s="137">
-        <f>IFERROR(VLOOKUP(B215,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B215,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>651.34</v>
       </c>
       <c r="D215" s="129"/>
@@ -9902,8 +9765,7 @@
         <v>487</v>
       </c>
       <c r="C216" s="137">
-        <f>IFERROR(VLOOKUP(B216,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B216,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D216" s="129"/>
       <c r="E216" s="129"/>
@@ -9919,7 +9781,7 @@
         <v>488</v>
       </c>
       <c r="C217" s="137">
-        <f>IFERROR(VLOOKUP(B217,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B217,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>-3057.96</v>
       </c>
       <c r="D217" s="129"/>
@@ -9936,8 +9798,7 @@
         <v>489</v>
       </c>
       <c r="C218" s="137">
-        <f>IFERROR(VLOOKUP(B218,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B218,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D218" s="129"/>
       <c r="E218" s="129"/>
@@ -9953,8 +9814,7 @@
         <v>490</v>
       </c>
       <c r="C219" s="137">
-        <f>IFERROR(VLOOKUP(B219,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B219,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D219" s="129"/>
       <c r="E219" s="129"/>
@@ -9970,8 +9830,7 @@
         <v>491</v>
       </c>
       <c r="C220" s="137">
-        <f>IFERROR(VLOOKUP(B220,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B220,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D220" s="129"/>
       <c r="E220" s="129"/>
@@ -9987,8 +9846,7 @@
         <v>492</v>
       </c>
       <c r="C221" s="137">
-        <f>IFERROR(VLOOKUP(B221,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B221,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D221" s="129"/>
       <c r="E221" s="129"/>
@@ -10004,8 +9862,7 @@
         <v>493</v>
       </c>
       <c r="C222" s="137">
-        <f>IFERROR(VLOOKUP(B222,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B222,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D222" s="129"/>
       <c r="E222" s="129"/>
@@ -10021,7 +9878,7 @@
         <v>494</v>
       </c>
       <c r="C223" s="137">
-        <f>IFERROR(VLOOKUP(B223,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B223,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>34732.29</v>
       </c>
       <c r="D223" s="129"/>
@@ -10038,8 +9895,7 @@
         <v>495</v>
       </c>
       <c r="C224" s="137">
-        <f>IFERROR(VLOOKUP(B224,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B224,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D224" s="129"/>
       <c r="E224" s="129"/>
@@ -10055,8 +9911,7 @@
         <v>496</v>
       </c>
       <c r="C225" s="137">
-        <f>IFERROR(VLOOKUP(B225,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B225,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D225" s="129"/>
       <c r="E225" s="129"/>
@@ -10072,8 +9927,7 @@
         <v>497</v>
       </c>
       <c r="C226" s="137">
-        <f>IFERROR(VLOOKUP(B226,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B226,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D226" s="129"/>
       <c r="E226" s="129"/>
@@ -10089,8 +9943,7 @@
         <v>498</v>
       </c>
       <c r="C227" s="137">
-        <f>IFERROR(VLOOKUP(B227,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B227,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D227" s="129"/>
       <c r="E227" s="129"/>
@@ -10106,8 +9959,7 @@
         <v>499</v>
       </c>
       <c r="C228" s="137">
-        <f>IFERROR(VLOOKUP(B228,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B228,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D228" s="129"/>
       <c r="E228" s="129"/>
@@ -10123,8 +9975,7 @@
         <v>500</v>
       </c>
       <c r="C229" s="137">
-        <f>IFERROR(VLOOKUP(B229,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B229,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D229" s="129"/>
       <c r="E229" s="129"/>
@@ -10140,8 +9991,7 @@
         <v>501</v>
       </c>
       <c r="C230" s="137">
-        <f>IFERROR(VLOOKUP(B230,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B230,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D230" s="129"/>
       <c r="E230" s="129"/>
@@ -10157,8 +10007,7 @@
         <v>502</v>
       </c>
       <c r="C231" s="137">
-        <f>IFERROR(VLOOKUP(B231,Hoja1!$A$27:$D$450,4,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(B231,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
       </c>
       <c r="D231" s="129"/>
       <c r="E231" s="129"/>
@@ -10174,7 +10023,7 @@
         <v>503</v>
       </c>
       <c r="C232" s="137">
-        <f>IFERROR(VLOOKUP(B232,Hoja1!$A$27:$D$450,4,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(B232,'Balance de sumas y saldos'!$A$27:$D$450,4,FALSE),)</f>
         <v>4965.52</v>
       </c>
       <c r="D232" s="129"/>
@@ -14166,7 +14015,7 @@
         <v>973.2200000000303</v>
       </c>
       <c r="J15" s="99">
-        <f>-SALDOS!C45</f>
+        <f>-'Distribución por línea'!C45</f>
         <v>110762.6</v>
       </c>
       <c r="K15" s="101">
@@ -14209,7 +14058,7 @@
         <v>2368.6699999999546</v>
       </c>
       <c r="J16" s="99">
-        <f>-SALDOS!C53</f>
+        <f>-'Distribución por línea'!C53</f>
         <v>127115.9</v>
       </c>
       <c r="K16" s="101">
@@ -14252,7 +14101,7 @@
         <v>206.07000000007247</v>
       </c>
       <c r="J17" s="99">
-        <f>-SALDOS!C46</f>
+        <f>-'Distribución por línea'!C46</f>
         <v>55642.59</v>
       </c>
       <c r="K17" s="101">
@@ -14294,7 +14143,7 @@
         <v>406.9699999999648</v>
       </c>
       <c r="J18" s="99">
-        <f>-SALDOS!C47</f>
+        <f>-'Distribución por línea'!C47</f>
         <v>23489.12</v>
       </c>
       <c r="K18" s="101">
@@ -14336,7 +14185,7 @@
         <v>1758.7399999999907</v>
       </c>
       <c r="J19" s="99">
-        <f>-SALDOS!C49</f>
+        <f>-'Distribución por línea'!C49</f>
         <v>67464.69</v>
       </c>
       <c r="K19" s="101">
@@ -14420,7 +14269,7 @@
         <v>6369.749999999884</v>
       </c>
       <c r="J21" s="99">
-        <f>-SALDOS!C51</f>
+        <f>-'Distribución por línea'!C51</f>
         <v>266119.74</v>
       </c>
       <c r="K21" s="101">
@@ -14462,7 +14311,7 @@
         <v>295.4499999999989</v>
       </c>
       <c r="J22" s="99">
-        <f>-SALDOS!C55</f>
+        <f>-'Distribución por línea'!C55</f>
         <v>5701.57</v>
       </c>
       <c r="K22" s="101">
@@ -22749,8 +22598,7 @@
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="12">
-        <f>+SALDOS!C3</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C3</f>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -22764,7 +22612,7 @@
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="12">
-        <f>+SALDOS!C4</f>
+        <f>+'Distribución por línea'!C4</f>
         <v>5746.23</v>
       </c>
       <c r="G9" s="1"/>
@@ -22779,7 +22627,7 @@
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="12">
-        <f>+SALDOS!C5</f>
+        <f>+'Distribución por línea'!C5</f>
         <v>7239.24</v>
       </c>
       <c r="G10" s="1"/>
@@ -22794,7 +22642,7 @@
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="12">
-        <f>+SALDOS!C7</f>
+        <f>+'Distribución por línea'!C7</f>
         <v>981.500000000146</v>
       </c>
       <c r="G11" s="1"/>
@@ -22809,7 +22657,7 @@
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="12">
-        <f>+SALDOS!C6</f>
+        <f>+'Distribución por línea'!C6</f>
         <v>-15.710000000018</v>
       </c>
       <c r="G12" s="21"/>
@@ -22824,8 +22672,7 @@
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="12">
-        <f>+SALDOS!C8</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C8</f>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -22839,7 +22686,7 @@
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="12">
-        <f>+SALDOS!C9</f>
+        <f>+'Distribución por línea'!C9</f>
         <v>2.66999999999998</v>
       </c>
       <c r="G14" s="1"/>
@@ -22854,8 +22701,7 @@
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="12">
-        <f>+SALDOS!C10</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C10</f>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -22869,8 +22715,7 @@
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="12">
-        <f>+SALDOS!C11</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C11</f>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -22923,8 +22768,7 @@
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="12">
-        <f>+SALDOS!C30</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C30</f>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -22938,8 +22782,7 @@
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="67">
-        <f>+SALDOS!C12</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C12</f>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -22953,7 +22796,7 @@
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="67">
-        <f>+SALDOS!C13</f>
+        <f>+'Distribución por línea'!C13</f>
         <v>1132355.33</v>
       </c>
       <c r="G22" s="1"/>
@@ -22968,7 +22811,7 @@
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="67">
-        <f>+SALDOS!C16</f>
+        <f>+'Distribución por línea'!C16</f>
         <v>5340.7</v>
       </c>
       <c r="G23" s="1"/>
@@ -22983,7 +22826,7 @@
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="12">
-        <f>+SALDOS!C14</f>
+        <f>+'Distribución por línea'!C14</f>
         <v>-1.77635683940025e-15</v>
       </c>
       <c r="G24" s="1"/>
@@ -22998,7 +22841,7 @@
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="12">
-        <f>+SALDOS!C15</f>
+        <f>+'Distribución por línea'!C15</f>
         <v>-8.88178419700125e-16</v>
       </c>
       <c r="G25" s="1"/>
@@ -23013,7 +22856,7 @@
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="67">
-        <f>+SALDOS!C17</f>
+        <f>+'Distribución por línea'!C17</f>
         <v>35314.56</v>
       </c>
       <c r="G26" s="1"/>
@@ -23028,7 +22871,7 @@
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="67">
-        <f>+SALDOS!C18</f>
+        <f>+'Distribución por línea'!C18</f>
         <v>358.96</v>
       </c>
       <c r="G27" s="1"/>
@@ -23043,8 +22886,7 @@
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="67">
-        <f>+SALDOS!C23</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C23</f>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -23058,7 +22900,7 @@
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="67">
-        <f>+SALDOS!C24</f>
+        <f>+'Distribución por línea'!C24</f>
         <v>17670.09</v>
       </c>
       <c r="G29" s="1"/>
@@ -23073,8 +22915,7 @@
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="67">
-        <f>+SALDOS!C25</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C25</f>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -23088,7 +22929,7 @@
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="67">
-        <f>+SALDOS!C26</f>
+        <f>+'Distribución por línea'!C26</f>
         <v>65129.21</v>
       </c>
       <c r="G31" s="1"/>
@@ -23103,7 +22944,7 @@
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="67">
-        <f>+SALDOS!C27</f>
+        <f>+'Distribución por línea'!C27</f>
         <v>0.62</v>
       </c>
       <c r="G32" s="1"/>
@@ -23118,7 +22959,7 @@
       </c>
       <c r="E33" s="68"/>
       <c r="F33" s="12">
-        <f>+SALDOS!C38</f>
+        <f>+'Distribución por línea'!C38</f>
         <v>73.46</v>
       </c>
       <c r="G33" s="1"/>
@@ -23133,8 +22974,7 @@
       </c>
       <c r="E34" s="68"/>
       <c r="F34" s="12">
-        <f>+SALDOS!C36</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C36</f>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -23148,8 +22988,7 @@
       </c>
       <c r="E35" s="68"/>
       <c r="F35" s="12">
-        <f>+SALDOS!C31</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C31</f>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -23163,8 +23002,7 @@
       </c>
       <c r="E36" s="68"/>
       <c r="F36" s="12">
-        <f>+SALDOS!C32</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C32</f>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -23178,7 +23016,7 @@
       </c>
       <c r="E37" s="68"/>
       <c r="F37" s="12">
-        <f>+SALDOS!D61+SALDOS!C35</f>
+        <f>+'Distribución por línea'!D61+'Distribución por línea'!C35</f>
         <v>219.280000000001</v>
       </c>
       <c r="G37" s="1"/>
@@ -23193,8 +23031,7 @@
       </c>
       <c r="E38" s="68"/>
       <c r="F38" s="12">
-        <f>+SALDOS!C33</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C33</f>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -23208,7 +23045,7 @@
       </c>
       <c r="E39" s="68"/>
       <c r="F39" s="12">
-        <f>+SALDOS!C34</f>
+        <f>+'Distribución por línea'!C34</f>
         <v>11810.75</v>
       </c>
       <c r="G39" s="1"/>
@@ -23223,7 +23060,7 @@
       </c>
       <c r="E40" s="68"/>
       <c r="F40" s="12">
-        <f>+SALDOS!C28</f>
+        <f>+'Distribución por línea'!C28</f>
         <v>4529.05</v>
       </c>
       <c r="G40" s="1"/>
@@ -23238,8 +23075,7 @@
       </c>
       <c r="E41" s="68"/>
       <c r="F41" s="12">
-        <f>+SALDOS!C29</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C29</f>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -23253,8 +23089,7 @@
       </c>
       <c r="E42" s="68"/>
       <c r="F42" s="12">
-        <f>+SALDOS!C19</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C19</f>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -23268,7 +23103,7 @@
       </c>
       <c r="E43" s="68"/>
       <c r="F43" s="12">
-        <f>+SALDOS!C20</f>
+        <f>+'Distribución por línea'!C20</f>
         <v>165.44</v>
       </c>
       <c r="G43" s="1"/>
@@ -23283,7 +23118,7 @@
       </c>
       <c r="E44" s="68"/>
       <c r="F44" s="12">
-        <f>+SALDOS!C21</f>
+        <f>+'Distribución por línea'!C21</f>
         <v>138.22</v>
       </c>
       <c r="G44" s="1"/>
@@ -23298,7 +23133,7 @@
       </c>
       <c r="E45" s="68"/>
       <c r="F45" s="12">
-        <f>+SALDOS!C22</f>
+        <f>+'Distribución por línea'!C22</f>
         <v>1214719.33</v>
       </c>
       <c r="G45" s="1"/>
@@ -23313,7 +23148,7 @@
       </c>
       <c r="E46" s="68"/>
       <c r="F46" s="12">
-        <f>+SALDOS!C56</f>
+        <f>+'Distribución por línea'!C56</f>
         <v>165358.57</v>
       </c>
       <c r="G46" s="1"/>
@@ -23328,7 +23163,7 @@
       </c>
       <c r="E47" s="68"/>
       <c r="F47" s="12">
-        <f>+SALDOS!C57</f>
+        <f>+'Distribución por línea'!C57</f>
         <v>1063586.36</v>
       </c>
       <c r="G47" s="1"/>
@@ -23380,7 +23215,7 @@
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="12">
-        <f>+SALDOS!C37</f>
+        <f>+'Distribución por línea'!C37</f>
         <v>104684</v>
       </c>
       <c r="G51" s="1"/>
@@ -23456,8 +23291,7 @@
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="12">
-        <f>+SALDOS!C39</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!C39</f>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -23565,7 +23399,7 @@
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="12">
-        <f>-SALDOS!E61</f>
+        <f>-'Distribución por línea'!E61</f>
         <v>71988.8751050439</v>
       </c>
       <c r="G66" s="1"/>
@@ -23580,8 +23414,7 @@
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="12">
-        <f>-SALDOS!C91</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!C91</f>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -23622,7 +23455,7 @@
       </c>
       <c r="E70" s="69"/>
       <c r="F70" s="67">
-        <f>-SALDOS!C86</f>
+        <f>-'Distribución por línea'!C86</f>
         <v>134391.6</v>
       </c>
       <c r="G70" s="1"/>
@@ -23637,7 +23470,7 @@
       </c>
       <c r="E71" s="69"/>
       <c r="F71" s="67">
-        <f>-SALDOS!C96</f>
+        <f>-'Distribución por línea'!C96</f>
         <v>3.90798504668055e-14</v>
       </c>
       <c r="G71" s="1"/>
@@ -23652,8 +23485,7 @@
       </c>
       <c r="E72" s="69"/>
       <c r="F72" s="67">
-        <f>-SALDOS!C85</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!C85</f>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -23667,8 +23499,7 @@
       </c>
       <c r="E73" s="69"/>
       <c r="F73" s="67">
-        <f>-SALDOS!C90</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!C90</f>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -23682,8 +23513,7 @@
       </c>
       <c r="E74" s="69"/>
       <c r="F74" s="67">
-        <f>-SALDOS!C88</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!C88</f>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -23697,7 +23527,7 @@
       </c>
       <c r="E75" s="69"/>
       <c r="F75" s="67">
-        <f>-SALDOS!C93</f>
+        <f>-'Distribución por línea'!C93</f>
         <v>13.32</v>
       </c>
       <c r="G75" s="1"/>
@@ -23726,7 +23556,7 @@
       </c>
       <c r="E77" s="69"/>
       <c r="F77" s="67">
-        <f>-SALDOS!C95</f>
+        <f>-'Distribución por línea'!C95</f>
         <v>0.900000000000002</v>
       </c>
       <c r="G77" s="1"/>
@@ -23741,7 +23571,7 @@
       </c>
       <c r="E78" s="69"/>
       <c r="F78" s="67">
-        <f>-SALDOS!C80</f>
+        <f>-'Distribución por línea'!C80</f>
         <v>1208275.2</v>
       </c>
       <c r="G78" s="1"/>
@@ -23756,7 +23586,7 @@
       </c>
       <c r="E79" s="69"/>
       <c r="F79" s="67">
-        <f>-SALDOS!C81</f>
+        <f>-'Distribución por línea'!C81</f>
         <v>521.21</v>
       </c>
       <c r="G79" s="1"/>
@@ -23771,7 +23601,7 @@
       </c>
       <c r="E80" s="69"/>
       <c r="F80" s="67">
-        <f>-SALDOS!C82</f>
+        <f>-'Distribución por línea'!C82</f>
         <v>25741.92</v>
       </c>
       <c r="G80" s="1"/>
@@ -23823,7 +23653,7 @@
       </c>
       <c r="E84" s="69"/>
       <c r="F84" s="67">
-        <f>-SALDOS!C83</f>
+        <f>-'Distribución por línea'!C83</f>
         <v>31629.29</v>
       </c>
       <c r="G84" s="1"/>
@@ -23838,7 +23668,7 @@
       </c>
       <c r="E85" s="69"/>
       <c r="F85" s="12">
-        <f>-SALDOS!C87</f>
+        <f>-'Distribución por línea'!C87</f>
         <v>26660.31</v>
       </c>
       <c r="G85" s="1"/>
@@ -23853,8 +23683,7 @@
       </c>
       <c r="E86" s="69"/>
       <c r="F86" s="12">
-        <f>-SALDOS!C92</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!C92</f>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
@@ -23868,8 +23697,7 @@
       </c>
       <c r="E87" s="69"/>
       <c r="F87" s="70">
-        <f>-SALDOS!C89</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!C89</f>
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
@@ -24965,7 +24793,7 @@
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="32">
-        <f>-SALDOS!C149-SALDOS!C109</f>
+        <f>-'Distribución por línea'!C149-'Distribución por línea'!C109</f>
         <v>-46243.8675605284</v>
       </c>
       <c r="D17" s="1"/>
@@ -24978,8 +24806,7 @@
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="32">
-        <f>-SALDOS!C112</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!C112</f>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="12"/>
@@ -24991,8 +24818,7 @@
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="32">
-        <f>-SALDOS!C208</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!C208</f>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="12"/>
